--- a/JsonConverter/ExcelFiles/ConfirmData.xlsx
+++ b/JsonConverter/ExcelFiles/ConfirmData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
   <si>
     <t>제목</t>
   </si>
@@ -51,29 +51,35 @@
     <t>ConfirmType</t>
   </si>
   <si>
-    <t>TEST_CONFIRM</t>
-  </si>
-  <si>
-    <t>test title</t>
-  </si>
-  <si>
-    <t>test desc</t>
-  </si>
-  <si>
-    <t>test OK</t>
-  </si>
-  <si>
-    <t>test Cancel</t>
-  </si>
-  <si>
-    <t>OK_CANCEL</t>
+    <t>LoginFail</t>
+  </si>
+  <si>
+    <t>로그인 실패</t>
+  </si>
+  <si>
+    <t>다시 시도해 주세요.</t>
+  </si>
+  <si>
+    <t>확인</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>SignUpFail</t>
+  </si>
+  <si>
+    <t>회원가입 실패</t>
+  </si>
+  <si>
+    <t>다시 시도해 주세요</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -82,6 +88,11 @@
     </font>
     <font>
       <b/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -101,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -110,6 +121,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -327,6 +341,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="16.38"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1"/>
@@ -387,23 +404,37 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="2" t="s">
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
         <v>17</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/JsonConverter/ExcelFiles/ConfirmData.xlsx
+++ b/JsonConverter/ExcelFiles/ConfirmData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="23">
   <si>
     <t>제목</t>
   </si>
@@ -73,6 +73,15 @@
   </si>
   <si>
     <t>다시 시도해 주세요</t>
+  </si>
+  <si>
+    <t>Default_Equipment</t>
+  </si>
+  <si>
+    <t>장착 해제 불가</t>
+  </si>
+  <si>
+    <t>기본 장비는 장착 해제할 수 없습니다</t>
   </si>
 </sst>
 </file>
@@ -343,6 +352,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="16.38"/>
+    <col customWidth="1" min="3" max="3" width="36.38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -437,6 +447,23 @@
         <v>16</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
